--- a/ROSALES/Junio/expensas rosales JUNIOxlsx.xlsx
+++ b/ROSALES/Junio/expensas rosales JUNIOxlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B8C57F-BEE8-44DD-8338-91A4224AC1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AE606E-4B21-4258-AF41-6D2CB9122CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="134">
   <si>
     <t>TOTAL</t>
   </si>
@@ -383,12 +383,6 @@
     <t>Subidos en ABR 2025</t>
   </si>
   <si>
-    <t>Este mes y el anterior lo cerramos sin TSG - EL mes que viene hay que pasar 3</t>
-  </si>
-  <si>
-    <t>Desobstruccion de colectora pluvial</t>
-  </si>
-  <si>
     <t>Matias Salvatierra - Desobstruccion de colectora cloacal</t>
   </si>
   <si>
@@ -432,6 +426,9 @@
   </si>
   <si>
     <t>EGRESOS DEL MES DE JUNIO</t>
+  </si>
+  <si>
+    <t>Sebastian</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1127,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1461,9 +1458,6 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1495,6 +1489,13 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1945,10 +1946,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1997,11 +1998,11 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="33">
-        <v>41473</v>
+      <c r="C18" s="235">
+        <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
@@ -2011,8 +2012,8 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="218">
-        <v>307780.02</v>
+      <c r="C19" s="233">
+        <v>308535.11</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
@@ -2035,7 +2036,7 @@
       <c r="B21" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="234">
         <v>78682.460000000006</v>
       </c>
       <c r="D21" s="4"/>
@@ -2049,7 +2050,7 @@
       <c r="B22" s="41"/>
       <c r="C22" s="23">
         <f>SUM(C17:C21)</f>
-        <v>492935.48000000004</v>
+        <v>528871.56999999995</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2057,7 +2058,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="39"/>
-      <c r="C23" s="219"/>
+      <c r="C23" s="218"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
@@ -2075,7 +2076,7 @@
         <v>115</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="33">
+      <c r="C25" s="231">
         <v>5684</v>
       </c>
       <c r="D25" s="45"/>
@@ -2083,7 +2084,7 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="140" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B26" s="141"/>
       <c r="C26" s="33">
@@ -2094,7 +2095,7 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="214" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B27" s="141"/>
       <c r="C27" s="33">
@@ -2104,24 +2105,22 @@
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="214" t="s">
-        <v>119</v>
+      <c r="A28" s="232" t="s">
+        <v>133</v>
       </c>
       <c r="B28" s="141"/>
-      <c r="C28" s="33">
-        <v>76654</v>
+      <c r="C28" s="231">
+        <v>65000</v>
       </c>
       <c r="D28" s="45"/>
-      <c r="F28" s="12" t="s">
-        <v>118</v>
-      </c>
+      <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B29" s="42"/>
-      <c r="C29" s="33">
+      <c r="C29" s="231">
         <v>45000</v>
       </c>
       <c r="F29" s="12"/>
@@ -2141,7 +2140,7 @@
       <c r="B31" s="41"/>
       <c r="C31" s="23">
         <f>SUM(C23:C30)</f>
-        <v>553139.87</v>
+        <v>541485.87</v>
       </c>
       <c r="F31" s="12"/>
     </row>
@@ -2152,7 +2151,7 @@
       <c r="B32" s="30"/>
       <c r="C32" s="43">
         <f>+C31+C22</f>
-        <v>1046075.3500000001</v>
+        <v>1070357.44</v>
       </c>
       <c r="F32" s="12"/>
     </row>
@@ -2190,11 +2189,11 @@
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="220" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="220"/>
-      <c r="C39" s="221">
+      <c r="A39" s="219" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="219"/>
+      <c r="C39" s="220">
         <v>1000000</v>
       </c>
       <c r="F39" s="12"/>
@@ -2221,7 +2220,7 @@
       <c r="B43" s="18"/>
       <c r="C43" s="19">
         <f>+C41+C32</f>
-        <v>1046075.3500000001</v>
+        <v>1070357.44</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2241,7 +2240,7 @@
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="164" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B48" s="162"/>
       <c r="C48" s="165">
@@ -2252,12 +2251,12 @@
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="164" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B49" s="162"/>
       <c r="C49" s="167">
         <f>-(C32-C30)</f>
-        <v>-1046075.3500000001</v>
+        <v>-1070357.44</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -2283,7 +2282,7 @@
       <c r="B52" s="161"/>
       <c r="C52" s="170">
         <f>SUM(C46:C50)</f>
-        <v>-572529.8020046202</v>
+        <v>-596811.89200462005</v>
       </c>
       <c r="D52" s="5"/>
     </row>
@@ -2293,15 +2292,15 @@
       <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="222"/>
-      <c r="B54" s="222"/>
-      <c r="C54" s="222"/>
+      <c r="A54" s="221"/>
+      <c r="B54" s="221"/>
+      <c r="C54" s="221"/>
       <c r="F54" s="44"/>
     </row>
     <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="223"/>
-      <c r="B55" s="223"/>
-      <c r="C55" s="223"/>
+      <c r="A55" s="222"/>
+      <c r="B55" s="222"/>
+      <c r="C55" s="222"/>
     </row>
     <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
@@ -2400,23 +2399,23 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="224">
+        <v>124</v>
+      </c>
+      <c r="B1" s="223">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="224"/>
+      <c r="C1" s="223"/>
       <c r="D1" s="145">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G1" s="226">
+        <v>123</v>
+      </c>
+      <c r="G1" s="225">
         <v>1000000</v>
       </c>
-      <c r="H1" s="226"/>
+      <c r="H1" s="225"/>
     </row>
     <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -2444,10 +2443,10 @@
         <v>109</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K2" s="50" t="s">
         <v>17</v>
@@ -2503,7 +2502,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>35</v>
@@ -3579,62 +3578,62 @@
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="225" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="225"/>
-      <c r="C33" s="225"/>
-      <c r="D33" s="225"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
-      <c r="G33" s="225"/>
-      <c r="H33" s="225"/>
-      <c r="I33" s="225"/>
-      <c r="J33" s="225"/>
-      <c r="K33" s="225"/>
-      <c r="L33" s="225"/>
+      <c r="A33" s="224" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="224"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="224"/>
+      <c r="E33" s="224"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="224"/>
+      <c r="H33" s="224"/>
+      <c r="I33" s="224"/>
+      <c r="J33" s="224"/>
+      <c r="K33" s="224"/>
+      <c r="L33" s="224"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="225"/>
-      <c r="B34" s="225"/>
-      <c r="C34" s="225"/>
-      <c r="D34" s="225"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
-      <c r="G34" s="225"/>
-      <c r="H34" s="225"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
-      <c r="K34" s="225"/>
-      <c r="L34" s="225"/>
+      <c r="A34" s="224"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="224"/>
+      <c r="L34" s="224"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="225"/>
-      <c r="B35" s="225"/>
-      <c r="C35" s="225"/>
-      <c r="D35" s="225"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
-      <c r="G35" s="225"/>
-      <c r="H35" s="225"/>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="225"/>
-      <c r="L35" s="225"/>
+      <c r="A35" s="224"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="224"/>
+      <c r="J35" s="224"/>
+      <c r="K35" s="224"/>
+      <c r="L35" s="224"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="225"/>
-      <c r="B36" s="225"/>
-      <c r="C36" s="225"/>
-      <c r="D36" s="225"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
-      <c r="G36" s="225"/>
-      <c r="H36" s="225"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="225"/>
-      <c r="K36" s="225"/>
-      <c r="L36" s="225"/>
+      <c r="A36" s="224"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="224"/>
+      <c r="J36" s="224"/>
+      <c r="K36" s="224"/>
+      <c r="L36" s="224"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3674,22 +3673,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="227" t="s">
+      <c r="A1" s="226" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="228"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="228"/>
-      <c r="F1" s="228"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="228"/>
-      <c r="I1" s="228"/>
-      <c r="J1" s="228"/>
-      <c r="K1" s="228"/>
-      <c r="L1" s="228"/>
-      <c r="M1" s="228"/>
-      <c r="N1" s="229"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="228"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -3790,7 +3789,7 @@
         <v>79</v>
       </c>
       <c r="C7" s="213">
-        <v>804174.23</v>
+        <v>265595.11</v>
       </c>
       <c r="D7" s="28"/>
       <c r="E7" s="177"/>
@@ -3827,11 +3826,11 @@
         <f>C8-J38</f>
         <v>-159634.85269999999</v>
       </c>
-      <c r="L8" s="231">
+      <c r="L8" s="230">
         <f>C7-J38</f>
-        <v>644539.37730000005</v>
-      </c>
-      <c r="M8" s="231"/>
+        <v>105960.2573</v>
+      </c>
+      <c r="M8" s="230"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -3921,7 +3920,7 @@
       </c>
       <c r="L10" s="129">
         <f>L$8*E10/S$12</f>
-        <v>32935.962180030008</v>
+        <v>5414.5691480300002</v>
       </c>
       <c r="M10" s="109">
         <f>G10-F10</f>
@@ -3929,11 +3928,11 @@
       </c>
       <c r="N10" s="106">
         <f>J10+L10</f>
-        <v>43627.680180030009</v>
+        <v>16106.287148030002</v>
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>168114.72596103002</v>
+        <v>140593.33292903</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -3977,7 +3976,7 @@
       </c>
       <c r="L11" s="129">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>32807.054304570003</v>
+        <v>5393.3770965700005</v>
       </c>
       <c r="M11" s="109">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
@@ -3985,11 +3984,11 @@
       </c>
       <c r="N11" s="106">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>39259.599904569979</v>
+        <v>11845.922696569975</v>
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>163259.41654356997</v>
+        <v>135845.73933556996</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4033,7 +4032,7 @@
       </c>
       <c r="L12" s="129">
         <f t="shared" si="3"/>
-        <v>32484.784615920005</v>
+        <v>5340.39696792</v>
       </c>
       <c r="M12" s="109">
         <f>G12-F12</f>
@@ -4041,11 +4040,11 @@
       </c>
       <c r="N12" s="106">
         <f t="shared" si="5"/>
-        <v>36639.548715919998</v>
+        <v>9495.1610679199948</v>
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>234698.30603527999</v>
+        <v>207553.91838727996</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4092,7 +4091,7 @@
       </c>
       <c r="L13" s="129">
         <f t="shared" si="3"/>
-        <v>33580.501557329997</v>
+        <v>5520.5294053299995</v>
       </c>
       <c r="M13" s="184">
         <f t="shared" si="4"/>
@@ -4100,11 +4099,11 @@
       </c>
       <c r="N13" s="106">
         <f t="shared" si="5"/>
-        <v>41599.290057329999</v>
+        <v>13539.317905330001</v>
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>168522.48154832999</v>
+        <v>140462.50939633002</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4148,7 +4147,7 @@
       </c>
       <c r="L14" s="129">
         <f t="shared" si="3"/>
-        <v>32935.962180030008</v>
+        <v>5414.5691480300002</v>
       </c>
       <c r="M14" s="109">
         <f t="shared" si="4"/>
@@ -4156,11 +4155,11 @@
       </c>
       <c r="N14" s="106">
         <f t="shared" si="5"/>
-        <v>40748.419280030008</v>
+        <v>13227.026248029997</v>
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>241557.99267327003</v>
+        <v>214036.59964127</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4204,7 +4203,7 @@
       </c>
       <c r="L15" s="129">
         <f t="shared" si="3"/>
-        <v>32807.054304570003</v>
+        <v>5393.3770965700005</v>
       </c>
       <c r="M15" s="109">
         <f t="shared" si="4"/>
@@ -4212,11 +4211,11 @@
       </c>
       <c r="N15" s="106">
         <f t="shared" si="5"/>
-        <v>36070.841904570021</v>
+        <v>8657.1646965700184</v>
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>160070.65854357003</v>
+        <v>132656.98133557002</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4259,7 +4258,7 @@
       </c>
       <c r="L16" s="129">
         <f t="shared" si="3"/>
-        <v>32935.962180030008</v>
+        <v>5414.5691480300002</v>
       </c>
       <c r="M16" s="109">
         <f t="shared" si="4"/>
@@ -4267,11 +4266,11 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" si="5"/>
-        <v>40241.96948003002</v>
+        <v>12720.576448030009</v>
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>164729.01526103003</v>
+        <v>137207.62222903001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4314,7 +4313,7 @@
       </c>
       <c r="L17" s="206">
         <f t="shared" si="3"/>
-        <v>32807.054304570003</v>
+        <v>5393.3770965700005</v>
       </c>
       <c r="M17" s="207">
         <f t="shared" si="4"/>
@@ -4322,11 +4321,11 @@
       </c>
       <c r="N17" s="202">
         <f t="shared" si="5"/>
-        <v>43742.618504569997</v>
+        <v>16328.941296569992</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>521744.13431033195</v>
+        <v>494330.45710233197</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4369,7 +4368,7 @@
       </c>
       <c r="L18" s="129">
         <f t="shared" si="3"/>
-        <v>32484.784615920005</v>
+        <v>5340.39696792</v>
       </c>
       <c r="M18" s="109">
         <f t="shared" si="4"/>
@@ -4377,11 +4376,11 @@
       </c>
       <c r="N18" s="106">
         <f t="shared" si="5"/>
-        <v>41600.881015920007</v>
+        <v>14456.493367920004</v>
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>164382.62479992001</v>
+        <v>137238.23715191998</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4424,7 +4423,7 @@
       </c>
       <c r="L19" s="129">
         <f t="shared" si="3"/>
-        <v>33580.501557329997</v>
+        <v>5520.5294053299995</v>
       </c>
       <c r="M19" s="109">
         <f>G19-F19</f>
@@ -4432,11 +4431,11 @@
       </c>
       <c r="N19" s="106">
         <f t="shared" si="5"/>
-        <v>54663.81915732997</v>
+        <v>26603.847005329975</v>
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>181587.01064832998</v>
+        <v>153527.03849632997</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4479,7 +4478,7 @@
       </c>
       <c r="L20" s="129">
         <f t="shared" si="3"/>
-        <v>32935.962180030008</v>
+        <v>5414.5691480300002</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="4"/>
@@ -4487,11 +4486,11 @@
       </c>
       <c r="N20" s="106">
         <f t="shared" si="5"/>
-        <v>48804.722580029993</v>
+        <v>21283.329548029986</v>
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>173291.76836103</v>
+        <v>145770.37532902998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4534,7 +4533,7 @@
       </c>
       <c r="L21" s="129">
         <f t="shared" si="3"/>
-        <v>32807.054304570003</v>
+        <v>5393.3770965700005</v>
       </c>
       <c r="M21" s="109">
         <f t="shared" si="4"/>
@@ -4542,11 +4541,11 @@
       </c>
       <c r="N21" s="106">
         <f t="shared" si="5"/>
-        <v>32807.054304570003</v>
+        <v>5393.3770965700005</v>
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>232830.68024813</v>
+        <v>205417.00304013002</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4589,7 +4588,7 @@
       </c>
       <c r="L22" s="129">
         <f t="shared" si="3"/>
-        <v>32484.784615920005</v>
+        <v>5340.39696792</v>
       </c>
       <c r="M22" s="109">
         <f t="shared" si="4"/>
@@ -4597,11 +4596,11 @@
       </c>
       <c r="N22" s="106">
         <f t="shared" si="5"/>
-        <v>40175.318615920005</v>
+        <v>13030.930967920001</v>
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>162957.06239991999</v>
+        <v>135812.67475191999</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4644,7 +4643,7 @@
       </c>
       <c r="L23" s="129">
         <f t="shared" si="3"/>
-        <v>33580.501557329997</v>
+        <v>5520.5294053299995</v>
       </c>
       <c r="M23" s="109">
         <f t="shared" si="4"/>
@@ -4652,11 +4651,11 @@
       </c>
       <c r="N23" s="106">
         <f t="shared" si="5"/>
-        <v>47657.93025733003</v>
+        <v>19597.958105330035</v>
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>252397.24089897005</v>
+        <v>224337.26874697005</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4699,7 +4698,7 @@
       </c>
       <c r="L24" s="129">
         <f t="shared" si="3"/>
-        <v>32484.784615920005</v>
+        <v>5340.39696792</v>
       </c>
       <c r="M24" s="109">
         <f t="shared" si="4"/>
@@ -4707,11 +4706,11 @@
       </c>
       <c r="N24" s="106">
         <f t="shared" si="5"/>
-        <v>38777.892315919999</v>
+        <v>11633.504667919991</v>
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>161559.63609992</v>
+        <v>134415.24845191999</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -4754,7 +4753,7 @@
       </c>
       <c r="L25" s="129">
         <f t="shared" si="3"/>
-        <v>33580.501557329997</v>
+        <v>5520.5294053299995</v>
       </c>
       <c r="M25" s="109">
         <f t="shared" si="4"/>
@@ -4762,11 +4761,11 @@
       </c>
       <c r="N25" s="106">
         <f t="shared" si="5"/>
-        <v>42940.444157329992</v>
+        <v>14880.472005329997</v>
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>169863.63564833</v>
+        <v>141803.66349633</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4809,7 +4808,7 @@
       </c>
       <c r="L26" s="129">
         <f t="shared" si="3"/>
-        <v>47695.913920200001</v>
+        <v>7841.0590401999998</v>
       </c>
       <c r="M26" s="109">
         <f t="shared" si="4"/>
@@ -4817,11 +4816,11 @@
       </c>
       <c r="N26" s="106">
         <f>J26+L26</f>
-        <v>65205.946820199984</v>
+        <v>25351.091940199985</v>
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>245480.72936019997</v>
+        <v>205625.87448019997</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4854,18 +4853,18 @@
       <c r="K27" s="205"/>
       <c r="L27" s="206">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M27" s="207">
         <v>0</v>
       </c>
       <c r="N27" s="202">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>108383.74375621974</v>
+        <v>102567.08926021976</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4893,18 +4892,18 @@
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M28" s="109">
         <v>0</v>
       </c>
       <c r="N28" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>49402.187557559999</v>
+        <v>43585.533061559996</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -4925,18 +4924,18 @@
       <c r="K29" s="155"/>
       <c r="L29" s="156">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M29" s="157">
         <v>0</v>
       </c>
       <c r="N29" s="154">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>108383.74375621974</v>
+        <v>102567.08926021976</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -4957,18 +4956,18 @@
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M30" s="109">
         <v>0</v>
       </c>
       <c r="N30" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>49402.187557559999</v>
+        <v>43585.533061559996</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -4989,18 +4988,18 @@
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M31" s="109">
         <v>0</v>
       </c>
       <c r="N31" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>33271.398942840002</v>
+        <v>27454.744446839999</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -5021,18 +5020,18 @@
       <c r="K32" s="115"/>
       <c r="L32" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M32" s="109">
         <v>0</v>
       </c>
       <c r="N32" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>49402.187557559999</v>
+        <v>43585.533061559996</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -5053,18 +5052,18 @@
       <c r="K33" s="115"/>
       <c r="L33" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M33" s="109">
         <v>0</v>
       </c>
       <c r="N33" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>33271.398942840002</v>
+        <v>27454.744446839999</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -5085,18 +5084,18 @@
       <c r="K34" s="115"/>
       <c r="L34" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M34" s="109">
         <v>0</v>
       </c>
       <c r="N34" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>33271.398942840002</v>
+        <v>27454.744446839999</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5124,18 +5123,18 @@
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M35" s="109">
         <v>0</v>
       </c>
       <c r="N35" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>49402.187557559999</v>
+        <v>43585.533061559996</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5163,18 +5162,18 @@
       <c r="K36" s="108"/>
       <c r="L36" s="129">
         <f t="shared" si="3"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="M36" s="109">
         <v>0</v>
       </c>
       <c r="N36" s="106">
         <f t="shared" si="6"/>
-        <v>6961.0252748400007</v>
+        <v>1144.37077884</v>
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>33271.398942840002</v>
+        <v>27454.744446839999</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5226,12 +5225,12 @@
       <c r="K38" s="115"/>
       <c r="L38" s="115">
         <f>SUM(L10:L37)</f>
-        <v>644539.37729999947</v>
+        <v>105960.25730000007</v>
       </c>
       <c r="M38" s="116"/>
       <c r="N38" s="112">
         <f>SUM(N10:N37)</f>
-        <v>804174.22999999952</v>
+        <v>265595.10999999993</v>
       </c>
       <c r="P38" s="44"/>
     </row>
@@ -5254,7 +5253,7 @@
       <c r="K39" s="96"/>
       <c r="L39" s="135">
         <f>L38+J38</f>
-        <v>804174.22999999952</v>
+        <v>265595.11000000004</v>
       </c>
       <c r="M39" s="95"/>
       <c r="N39" s="95"/>
@@ -5264,18 +5263,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="230"/>
-      <c r="D40" s="228"/>
-      <c r="E40" s="228"/>
-      <c r="F40" s="228"/>
-      <c r="G40" s="228"/>
-      <c r="H40" s="228"/>
-      <c r="I40" s="228"/>
-      <c r="J40" s="228"/>
-      <c r="K40" s="228"/>
-      <c r="L40" s="228"/>
-      <c r="M40" s="228"/>
-      <c r="N40" s="228"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="227"/>
+      <c r="E40" s="227"/>
+      <c r="F40" s="227"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
+      <c r="I40" s="227"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="227"/>
+      <c r="M40" s="227"/>
+      <c r="N40" s="227"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">

--- a/ROSALES/Junio/expensas rosales JUNIOxlsx.xlsx
+++ b/ROSALES/Junio/expensas rosales JUNIOxlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AE606E-4B21-4258-AF41-6D2CB9122CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEA691A-2BEE-4F4E-B9FD-5BFA9B107906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="135">
   <si>
     <t>TOTAL</t>
   </si>
@@ -383,12 +383,6 @@
     <t>Subidos en ABR 2025</t>
   </si>
   <si>
-    <t>Matias Salvatierra - Desobstruccion de colectora cloacal</t>
-  </si>
-  <si>
-    <t>Casa Koruk - Botas de encargada</t>
-  </si>
-  <si>
     <t>CAJA ANTERIOR</t>
   </si>
   <si>
@@ -428,7 +422,16 @@
     <t>EGRESOS DEL MES DE JUNIO</t>
   </si>
   <si>
-    <t>Sebastian</t>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Recarga matafuegos</t>
+  </si>
+  <si>
+    <t>Anabella</t>
+  </si>
+  <si>
+    <t>ARBA</t>
   </si>
 </sst>
 </file>
@@ -665,7 +668,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1127,7 +1129,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1348,7 +1350,6 @@
     <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -1418,8 +1419,6 @@
     </xf>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1451,7 +1450,6 @@
     <xf numFmtId="43" fontId="26" fillId="10" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="10" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1489,13 +1487,11 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="31" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1579,12 +1575,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>790575</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2257425" cy="847725"/>
+    <xdr:ext cx="2333625" cy="1028699"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="image1.jpg">
@@ -1604,8 +1600,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3657600" y="447674"/>
-          <a:ext cx="2257425" cy="847725"/>
+          <a:off x="3943350" y="304800"/>
+          <a:ext cx="2333625" cy="1028699"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1946,10 +1942,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1998,10 +1994,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="235">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
@@ -2012,7 +2008,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="233">
+      <c r="C19" s="228">
         <v>308535.11</v>
       </c>
       <c r="D19" s="20"/>
@@ -2020,107 +2016,108 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="33">
-        <v>65000</v>
+      <c r="C20" s="228">
+        <v>197132.7</v>
       </c>
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="33">
+        <v>65000</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B22" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="234">
+      <c r="C22" s="33">
         <v>78682.460000000006</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="6"/>
-      <c r="F21" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="6"/>
+      <c r="F22" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="23">
-        <f>SUM(C17:C21)</f>
-        <v>528871.56999999995</v>
-      </c>
-    </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="23">
+        <f>SUM(C17:C22)</f>
+        <v>726004.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="218"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="33">
-        <v>349151.87</v>
-      </c>
-      <c r="D24" s="45"/>
-      <c r="F24" s="12"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="214"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B25" s="42"/>
-      <c r="C25" s="231">
-        <v>5684</v>
+      <c r="C25" s="33">
+        <v>349151.87</v>
       </c>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="140" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="141"/>
+      <c r="A26" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="42"/>
       <c r="C26" s="33">
-        <v>56650</v>
+        <f>C25/2</f>
+        <v>174575.935</v>
       </c>
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="214" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="141"/>
+      <c r="A27" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="42"/>
       <c r="C27" s="33">
-        <v>20000</v>
+        <v>5684</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="232" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="141"/>
-      <c r="C28" s="231">
-        <v>65000</v>
+      <c r="A28" s="210" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="140"/>
+      <c r="C28" s="33">
+        <v>275000</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B29" s="42"/>
-      <c r="C29" s="231">
+      <c r="C29" s="33">
         <v>45000</v>
       </c>
       <c r="F29" s="12"/>
@@ -2139,8 +2136,8 @@
       <c r="A31" s="40"/>
       <c r="B31" s="41"/>
       <c r="C31" s="23">
-        <f>SUM(C23:C30)</f>
-        <v>541485.87</v>
+        <f>SUM(C24:C30)</f>
+        <v>849411.80499999993</v>
       </c>
       <c r="F31" s="12"/>
     </row>
@@ -2150,8 +2147,8 @@
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="43">
-        <f>+C31+C22</f>
-        <v>1070357.44</v>
+        <f>+C31+C23</f>
+        <v>1575416.075</v>
       </c>
       <c r="F32" s="12"/>
     </row>
@@ -2189,11 +2186,11 @@
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="219" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="219"/>
-      <c r="C39" s="220">
+      <c r="A39" s="215" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="215"/>
+      <c r="C39" s="216">
         <v>1000000</v>
       </c>
       <c r="F39" s="12"/>
@@ -2220,7 +2217,7 @@
       <c r="B43" s="18"/>
       <c r="C43" s="19">
         <f>+C41+C32</f>
-        <v>1070357.44</v>
+        <v>1575416.075</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2228,61 +2225,61 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="C46" s="163"/>
+      <c r="C46" s="162"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
-      <c r="C47" s="163"/>
+      <c r="C47" s="162"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="164" t="s">
-        <v>120</v>
-      </c>
-      <c r="B48" s="162"/>
-      <c r="C48" s="165">
-        <v>-664175.24157355423</v>
+      <c r="A48" s="163" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="161"/>
+      <c r="C48" s="164">
+        <v>-572529.8020046202</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="164" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" s="162"/>
-      <c r="C49" s="167">
+      <c r="A49" s="163" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="161"/>
+      <c r="C49" s="166">
         <f>-(C32-C30)</f>
-        <v>-1070357.44</v>
+        <v>-1575416.075</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="164" t="s">
+      <c r="A50" s="163" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="162"/>
-      <c r="C50" s="211">
+      <c r="B50" s="161"/>
+      <c r="C50" s="208">
         <f>'prorrateo '!F31</f>
-        <v>1137720.7895689341</v>
+        <v>2012565.1348063203</v>
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="168"/>
-      <c r="C51" s="169"/>
+      <c r="A51" s="167"/>
+      <c r="C51" s="168"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="166" t="s">
+      <c r="A52" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="161"/>
-      <c r="C52" s="170">
+      <c r="B52" s="160"/>
+      <c r="C52" s="169">
         <f>SUM(C46:C50)</f>
-        <v>-596811.89200462005</v>
+        <v>-135380.74219829985</v>
       </c>
       <c r="D52" s="5"/>
     </row>
@@ -2292,15 +2289,15 @@
       <c r="C53" s="10"/>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="221"/>
-      <c r="B54" s="221"/>
-      <c r="C54" s="221"/>
+      <c r="A54" s="217"/>
+      <c r="B54" s="217"/>
+      <c r="C54" s="217"/>
       <c r="F54" s="44"/>
     </row>
     <row r="55" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="222"/>
-      <c r="B55" s="222"/>
-      <c r="C55" s="222"/>
+      <c r="A55" s="218"/>
+      <c r="B55" s="218"/>
+      <c r="C55" s="218"/>
     </row>
     <row r="56" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
@@ -2330,11 +2327,11 @@
       <c r="C59" s="32"/>
     </row>
     <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="171" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" s="172"/>
-      <c r="C60" s="173">
+      <c r="A60" s="170" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="171"/>
+      <c r="C60" s="172">
         <f>SUM(C56:C59)</f>
         <v>0</v>
       </c>
@@ -2399,23 +2396,23 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="223">
+        <v>122</v>
+      </c>
+      <c r="B1" s="219">
         <f>D1</f>
         <v>1436145.71</v>
       </c>
-      <c r="C1" s="223"/>
-      <c r="D1" s="145">
+      <c r="C1" s="219"/>
+      <c r="D1" s="144">
         <v>1436145.71</v>
       </c>
       <c r="E1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G1" s="225">
+        <v>121</v>
+      </c>
+      <c r="G1" s="221">
         <v>1000000</v>
       </c>
-      <c r="H1" s="225"/>
+      <c r="H1" s="221"/>
     </row>
     <row r="2" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -2443,10 +2440,10 @@
         <v>109</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K2" s="50" t="s">
         <v>17</v>
@@ -2469,11 +2466,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E3" s="131">
-        <v>73387.045781000008</v>
-      </c>
-      <c r="F3" s="215">
+        <v>124487.04578100001</v>
+      </c>
+      <c r="F3" s="211">
         <f>E3</f>
-        <v>73387.045781000008</v>
+        <v>124487.04578100001</v>
       </c>
       <c r="G3" s="56">
         <f>E3-F3</f>
@@ -2502,7 +2499,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>35</v>
@@ -2511,11 +2508,11 @@
         <v>5.09</v>
       </c>
       <c r="E4" s="131">
-        <v>73099.816638999997</v>
-      </c>
-      <c r="F4" s="215">
+        <v>123999.816639</v>
+      </c>
+      <c r="F4" s="211">
         <f t="shared" ref="F4:F18" si="0">E4</f>
-        <v>73099.816638999997</v>
+        <v>123999.816639</v>
       </c>
       <c r="G4" s="56">
         <f t="shared" ref="G4:G29" si="1">E4-F4</f>
@@ -2553,16 +2550,16 @@
         <v>5.04</v>
       </c>
       <c r="E5" s="131">
-        <v>72381.743783999991</v>
-      </c>
-      <c r="F5" s="215"/>
+        <v>198058.75731935998</v>
+      </c>
+      <c r="F5" s="211"/>
       <c r="G5" s="56">
         <f t="shared" si="1"/>
-        <v>72381.743783999991</v>
+        <v>198058.75731935998</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="2"/>
-        <v>2895.2697513599996</v>
+        <v>7922.3502927743993</v>
       </c>
       <c r="I5" s="56">
         <f t="shared" si="3"/>
@@ -2575,7 +2572,7 @@
       <c r="K5" s="56"/>
       <c r="L5" s="57">
         <f t="shared" si="5"/>
-        <v>198058.75731935998</v>
+        <v>328762.85139613436</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2590,19 +2587,19 @@
         <v>5.21</v>
       </c>
       <c r="E6" s="131">
-        <v>74823.191491000005</v>
-      </c>
-      <c r="F6" s="215">
-        <f>E6</f>
+        <v>126923.19149100001</v>
+      </c>
+      <c r="F6" s="211">
+        <f>E6-52100</f>
         <v>74823.191491000005</v>
       </c>
       <c r="G6" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>52100</v>
       </c>
       <c r="H6" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2084</v>
       </c>
       <c r="I6" s="56">
         <f t="shared" si="3"/>
@@ -2615,7 +2612,7 @@
       <c r="K6" s="56"/>
       <c r="L6" s="57">
         <f t="shared" si="5"/>
-        <v>126923.19149100001</v>
+        <v>181107.19149100001</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,16 +2629,19 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E7" s="131">
-        <v>73387.045781000008</v>
-      </c>
-      <c r="F7" s="215"/>
+        <v>200809.57339324002</v>
+      </c>
+      <c r="F7" s="211">
+        <f>E7</f>
+        <v>200809.57339324002</v>
+      </c>
       <c r="G7" s="56">
         <f t="shared" si="1"/>
-        <v>73387.045781000008</v>
+        <v>0</v>
       </c>
       <c r="H7" s="56">
         <f t="shared" si="2"/>
-        <v>2935.4818312400002</v>
+        <v>0</v>
       </c>
       <c r="I7" s="56">
         <f t="shared" si="3"/>
@@ -2654,7 +2654,7 @@
       <c r="K7" s="56"/>
       <c r="L7" s="57">
         <f t="shared" si="5"/>
-        <v>200809.57339324002</v>
+        <v>124487.04578100001</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2669,11 +2669,11 @@
         <v>5.09</v>
       </c>
       <c r="E8" s="131">
-        <v>73099.816638999997</v>
-      </c>
-      <c r="F8" s="215">
+        <v>123999.816639</v>
+      </c>
+      <c r="F8" s="211">
         <f>E8</f>
-        <v>73099.816638999997</v>
+        <v>123999.816639</v>
       </c>
       <c r="G8" s="56">
         <f t="shared" si="1"/>
@@ -2709,11 +2709,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E9" s="131">
-        <v>73387.045781000008</v>
-      </c>
-      <c r="F9" s="215">
+        <v>124487.04578100001</v>
+      </c>
+      <c r="F9" s="211">
         <f t="shared" si="0"/>
-        <v>73387.045781000008</v>
+        <v>124487.04578100001</v>
       </c>
       <c r="G9" s="56">
         <f t="shared" si="1"/>
@@ -2738,42 +2738,42 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="217" t="s">
+      <c r="A10" s="213" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="191" t="s">
+      <c r="B10" s="188" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="192" t="s">
+      <c r="C10" s="189" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="193">
+      <c r="D10" s="190">
         <v>5.09</v>
       </c>
-      <c r="E10" s="194">
-        <v>340386.24919880956</v>
-      </c>
-      <c r="F10" s="216"/>
-      <c r="G10" s="195">
+      <c r="E10" s="191">
+        <v>478001.51580576197</v>
+      </c>
+      <c r="F10" s="212"/>
+      <c r="G10" s="192">
         <f t="shared" si="1"/>
-        <v>340386.24919880956</v>
-      </c>
-      <c r="H10" s="195">
+        <v>478001.51580576197</v>
+      </c>
+      <c r="H10" s="192">
         <f t="shared" si="2"/>
-        <v>13615.449967952383</v>
-      </c>
-      <c r="I10" s="195">
+        <v>19120.060632230477</v>
+      </c>
+      <c r="I10" s="192">
         <f t="shared" si="3"/>
         <v>73099.816638999997</v>
       </c>
-      <c r="J10" s="195">
+      <c r="J10" s="192">
         <f t="shared" si="4"/>
         <v>50900</v>
       </c>
-      <c r="K10" s="195"/>
-      <c r="L10" s="196">
+      <c r="K10" s="192"/>
+      <c r="L10" s="193">
         <f t="shared" si="5"/>
-        <v>478001.51580576197</v>
+        <v>621121.39307699248</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -2788,11 +2788,11 @@
         <v>5.04</v>
       </c>
       <c r="E11" s="131">
-        <v>72381.743783999991</v>
-      </c>
-      <c r="F11" s="215">
+        <v>122781.74378399999</v>
+      </c>
+      <c r="F11" s="211">
         <f>E11</f>
-        <v>72381.743783999991</v>
+        <v>122781.74378399999</v>
       </c>
       <c r="G11" s="56">
         <f t="shared" si="1"/>
@@ -2828,11 +2828,11 @@
         <v>5.21</v>
       </c>
       <c r="E12" s="131">
-        <v>74823.191491000005</v>
-      </c>
-      <c r="F12" s="215">
+        <v>126923.19149100001</v>
+      </c>
+      <c r="F12" s="211">
         <f t="shared" si="0"/>
-        <v>74823.191491000005</v>
+        <v>126923.19149100001</v>
       </c>
       <c r="G12" s="56">
         <f t="shared" si="1"/>
@@ -2870,11 +2870,11 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="E13" s="131">
-        <v>73387.045781000008</v>
-      </c>
-      <c r="F13" s="215">
+        <v>124487.04578100001</v>
+      </c>
+      <c r="F13" s="211">
         <f>E13</f>
-        <v>73387.045781000008</v>
+        <v>124487.04578100001</v>
       </c>
       <c r="G13" s="56">
         <f t="shared" si="1"/>
@@ -2902,24 +2902,29 @@
       <c r="A14" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="142"/>
+      <c r="B14" s="141" t="s">
+        <v>133</v>
+      </c>
       <c r="C14" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="143">
+      <c r="D14" s="142">
         <v>5.09</v>
       </c>
       <c r="E14" s="131">
-        <v>73099.816638999997</v>
-      </c>
-      <c r="F14" s="215"/>
+        <v>200023.62594356001</v>
+      </c>
+      <c r="F14" s="211">
+        <f>130134.19-F25</f>
+        <v>87693.027717279998</v>
+      </c>
       <c r="G14" s="66">
         <f t="shared" si="1"/>
-        <v>73099.816638999997</v>
+        <v>112330.59822628001</v>
       </c>
       <c r="H14" s="66">
         <f t="shared" si="2"/>
-        <v>2923.9926655599998</v>
+        <v>4493.2239290512007</v>
       </c>
       <c r="I14" s="66">
         <f t="shared" si="3"/>
@@ -2930,9 +2935,9 @@
         <v>50900</v>
       </c>
       <c r="K14" s="66"/>
-      <c r="L14" s="144">
+      <c r="L14" s="143">
         <f t="shared" si="5"/>
-        <v>200023.62594356001</v>
+        <v>240823.6387943312</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2949,19 +2954,16 @@
         <v>5.04</v>
       </c>
       <c r="E15" s="131">
-        <v>214265.93077245081</v>
-      </c>
-      <c r="F15" s="215">
-        <f>E15</f>
-        <v>214265.93077245081</v>
-      </c>
+        <v>122781.74378399999</v>
+      </c>
+      <c r="F15" s="211"/>
       <c r="G15" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>122781.74378399999</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4911.2697513599996</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="3"/>
@@ -2974,7 +2976,7 @@
       <c r="K15" s="56"/>
       <c r="L15" s="57">
         <f t="shared" si="5"/>
-        <v>122781.74378399999</v>
+        <v>250474.75731935998</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2991,16 +2993,19 @@
         <v>5.21</v>
       </c>
       <c r="E16" s="131">
-        <v>74823.191491000005</v>
-      </c>
-      <c r="F16" s="215"/>
+        <v>204739.31064164001</v>
+      </c>
+      <c r="F16" s="211">
+        <f>E16-52100</f>
+        <v>152639.31064164001</v>
+      </c>
       <c r="G16" s="56">
         <f t="shared" si="1"/>
-        <v>74823.191491000005</v>
+        <v>52100</v>
       </c>
       <c r="H16" s="56">
         <f t="shared" si="2"/>
-        <v>2992.9276596400005</v>
+        <v>2084</v>
       </c>
       <c r="I16" s="56">
         <f t="shared" si="3"/>
@@ -3013,7 +3018,7 @@
       <c r="K16" s="56"/>
       <c r="L16" s="57">
         <f t="shared" si="5"/>
-        <v>204739.31064164001</v>
+        <v>181107.19149100001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -3028,11 +3033,11 @@
         <v>5.04</v>
       </c>
       <c r="E17" s="131">
-        <v>72381.743783999991</v>
-      </c>
-      <c r="F17" s="215">
+        <v>122781.74378399999</v>
+      </c>
+      <c r="F17" s="211">
         <f t="shared" si="0"/>
-        <v>72381.743783999991</v>
+        <v>122781.74378399999</v>
       </c>
       <c r="G17" s="56">
         <f t="shared" si="1"/>
@@ -3068,11 +3073,11 @@
         <v>5.21</v>
       </c>
       <c r="E18" s="131">
-        <v>74823.191491000005</v>
-      </c>
-      <c r="F18" s="215">
+        <v>126923.19149100001</v>
+      </c>
+      <c r="F18" s="211">
         <f t="shared" si="0"/>
-        <v>74823.191491000005</v>
+        <v>126923.19149100001</v>
       </c>
       <c r="G18" s="56">
         <f t="shared" si="1"/>
@@ -3108,11 +3113,11 @@
         <v>7.4</v>
       </c>
       <c r="E19" s="131">
-        <v>106274.78254</v>
-      </c>
-      <c r="F19" s="215">
+        <v>180274.78253999999</v>
+      </c>
+      <c r="F19" s="211">
         <f>E19</f>
-        <v>106274.78254</v>
+        <v>180274.78253999999</v>
       </c>
       <c r="G19" s="56">
         <f t="shared" si="1"/>
@@ -3137,42 +3142,42 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="190"/>
-      <c r="B20" s="191" t="s">
+      <c r="A20" s="187"/>
+      <c r="B20" s="188" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="192" t="s">
+      <c r="C20" s="189" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="193">
+      <c r="D20" s="190">
         <v>1.08</v>
       </c>
-      <c r="E20" s="194">
-        <v>72223.408474403608</v>
-      </c>
-      <c r="F20" s="216">
-        <v>0</v>
-      </c>
-      <c r="G20" s="195">
+      <c r="E20" s="191">
+        <v>101422.71848137975</v>
+      </c>
+      <c r="F20" s="212">
+        <v>0</v>
+      </c>
+      <c r="G20" s="192">
         <f t="shared" si="1"/>
-        <v>72223.408474403608</v>
-      </c>
-      <c r="H20" s="195">
+        <v>101422.71848137975</v>
+      </c>
+      <c r="H20" s="192">
         <f t="shared" si="2"/>
-        <v>2888.9363389761443</v>
-      </c>
-      <c r="I20" s="195">
+        <v>4056.9087392551901</v>
+      </c>
+      <c r="I20" s="192">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
-      <c r="J20" s="195">
+      <c r="J20" s="192">
         <f t="shared" si="4"/>
         <v>10800</v>
       </c>
-      <c r="K20" s="195"/>
-      <c r="L20" s="196">
+      <c r="K20" s="192"/>
+      <c r="L20" s="193">
         <f t="shared" si="5"/>
-        <v>101422.71848137975</v>
+        <v>131790.00088863494</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3187,16 +3192,19 @@
         <v>1.08</v>
       </c>
       <c r="E21" s="131">
-        <v>15510.373668</v>
-      </c>
-      <c r="F21" s="188"/>
+        <v>42441.162282719997</v>
+      </c>
+      <c r="F21" s="211">
+        <f>E21-10800</f>
+        <v>31641.162282719997</v>
+      </c>
       <c r="G21" s="56">
         <f t="shared" si="1"/>
-        <v>15510.373668</v>
+        <v>10800</v>
       </c>
       <c r="H21" s="56">
         <f t="shared" si="2"/>
-        <v>620.41494671999999</v>
+        <v>432</v>
       </c>
       <c r="I21" s="56">
         <f t="shared" si="3"/>
@@ -3209,44 +3217,44 @@
       <c r="K21" s="66"/>
       <c r="L21" s="57">
         <f t="shared" si="5"/>
-        <v>42441.162282719997</v>
+        <v>37542.373668</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="146"/>
-      <c r="B22" s="147"/>
-      <c r="C22" s="148" t="s">
+      <c r="A22" s="145"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="147" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="149">
+      <c r="D22" s="148">
         <v>1.08</v>
       </c>
-      <c r="E22" s="150">
-        <v>72223.408474403608</v>
-      </c>
-      <c r="F22" s="189">
-        <v>0</v>
-      </c>
-      <c r="G22" s="151">
+      <c r="E22" s="149">
+        <v>101422.71848137975</v>
+      </c>
+      <c r="F22" s="227">
+        <v>0</v>
+      </c>
+      <c r="G22" s="150">
         <f t="shared" si="1"/>
-        <v>72223.408474403608</v>
-      </c>
-      <c r="H22" s="151">
+        <v>101422.71848137975</v>
+      </c>
+      <c r="H22" s="150">
         <f t="shared" si="2"/>
-        <v>2888.9363389761443</v>
-      </c>
-      <c r="I22" s="151">
+        <v>4056.9087392551901</v>
+      </c>
+      <c r="I22" s="150">
         <f t="shared" si="3"/>
         <v>15510.373668</v>
       </c>
-      <c r="J22" s="151">
+      <c r="J22" s="150">
         <f t="shared" si="4"/>
         <v>10800</v>
       </c>
-      <c r="K22" s="151"/>
-      <c r="L22" s="152">
+      <c r="K22" s="150"/>
+      <c r="L22" s="151">
         <f t="shared" si="5"/>
-        <v>101422.71848137975</v>
+        <v>131790.00088863494</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3261,16 +3269,16 @@
         <v>1.08</v>
       </c>
       <c r="E23" s="131">
-        <v>15510.373668</v>
-      </c>
-      <c r="F23" s="188"/>
+        <v>42441.162282719997</v>
+      </c>
+      <c r="F23" s="211"/>
       <c r="G23" s="56">
         <f t="shared" si="1"/>
-        <v>15510.373668</v>
+        <v>42441.162282719997</v>
       </c>
       <c r="H23" s="56">
         <f t="shared" si="2"/>
-        <v>620.41494671999999</v>
+        <v>1697.6464913088</v>
       </c>
       <c r="I23" s="56">
         <f t="shared" si="3"/>
@@ -3283,7 +3291,7 @@
       <c r="K23" s="56"/>
       <c r="L23" s="57">
         <f t="shared" si="5"/>
-        <v>42441.162282719997</v>
+        <v>70449.182442028789</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3300,11 +3308,11 @@
         <v>1.08</v>
       </c>
       <c r="E24" s="131">
-        <v>15510.373668</v>
-      </c>
-      <c r="F24" s="215">
+        <v>26310.373668</v>
+      </c>
+      <c r="F24" s="211">
         <f>E24</f>
-        <v>15510.373668</v>
+        <v>26310.373668</v>
       </c>
       <c r="G24" s="56">
         <f t="shared" si="1"/>
@@ -3340,16 +3348,19 @@
         <v>1.08</v>
       </c>
       <c r="E25" s="131">
-        <v>15510.373668</v>
-      </c>
-      <c r="F25" s="215"/>
+        <v>42441.162282719997</v>
+      </c>
+      <c r="F25" s="211">
+        <f>E25</f>
+        <v>42441.162282719997</v>
+      </c>
       <c r="G25" s="56">
         <f t="shared" si="1"/>
-        <v>15510.373668</v>
+        <v>0</v>
       </c>
       <c r="H25" s="56">
         <f t="shared" si="2"/>
-        <v>620.41494671999999</v>
+        <v>0</v>
       </c>
       <c r="I25" s="56">
         <f t="shared" si="3"/>
@@ -3362,7 +3373,7 @@
       <c r="K25" s="56"/>
       <c r="L25" s="57">
         <f t="shared" si="5"/>
-        <v>42441.162282719997</v>
+        <v>26310.373668</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3377,11 +3388,11 @@
         <v>1.08</v>
       </c>
       <c r="E26" s="131">
-        <v>15510.373668</v>
-      </c>
-      <c r="F26" s="215">
-        <f t="shared" ref="F26:F27" si="6">E26</f>
-        <v>15510.373668</v>
+        <v>26310.373668</v>
+      </c>
+      <c r="F26" s="211">
+        <f t="shared" ref="F26:F28" si="6">E26</f>
+        <v>26310.373668</v>
       </c>
       <c r="G26" s="56">
         <f t="shared" si="1"/>
@@ -3417,11 +3428,11 @@
         <v>1.08</v>
       </c>
       <c r="E27" s="131">
-        <v>15510.373668</v>
-      </c>
-      <c r="F27" s="215">
+        <v>26310.373668</v>
+      </c>
+      <c r="F27" s="211">
         <f t="shared" si="6"/>
-        <v>15510.373668</v>
+        <v>26310.373668</v>
       </c>
       <c r="G27" s="56">
         <f t="shared" si="1"/>
@@ -3446,7 +3457,7 @@
       </c>
       <c r="O27" s="44">
         <f>F27+F26+F19</f>
-        <v>137295.52987600002</v>
+        <v>232895.52987599999</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -3462,16 +3473,19 @@
         <v>1.08</v>
       </c>
       <c r="E28" s="131">
-        <v>15510.373668</v>
-      </c>
-      <c r="F28" s="215"/>
+        <v>42441.162282719997</v>
+      </c>
+      <c r="F28" s="211">
+        <f t="shared" si="6"/>
+        <v>42441.162282719997</v>
+      </c>
       <c r="G28" s="56">
         <f t="shared" si="1"/>
-        <v>15510.373668</v>
+        <v>0</v>
       </c>
       <c r="H28" s="56">
         <f t="shared" si="2"/>
-        <v>620.41494671999999</v>
+        <v>0</v>
       </c>
       <c r="I28" s="56">
         <f t="shared" si="3"/>
@@ -3484,7 +3498,7 @@
       <c r="K28" s="56"/>
       <c r="L28" s="57">
         <f t="shared" si="5"/>
-        <v>42441.162282719997</v>
+        <v>26310.373668</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3501,19 +3515,16 @@
         <v>1.08</v>
       </c>
       <c r="E29" s="131">
-        <v>35055.122590483195</v>
-      </c>
-      <c r="F29" s="215">
-        <f>E29</f>
-        <v>35055.122590483195</v>
-      </c>
+        <v>26310.373668</v>
+      </c>
+      <c r="F29" s="211"/>
       <c r="G29" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26310.373668</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1052.41494672</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="3"/>
@@ -3526,7 +3537,7 @@
       <c r="K29" s="56"/>
       <c r="L29" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>53673.162282719997</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3556,7 +3567,7 @@
       <c r="E31" s="75"/>
       <c r="F31" s="137">
         <f>SUM(F3:F30)</f>
-        <v>1137720.7895689341</v>
+        <v>2012565.1348063203</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
@@ -3571,69 +3582,69 @@
       <c r="K31" s="137"/>
       <c r="L31" s="137">
         <f>SUM(L3:L29)</f>
-        <v>3310334.7228552024</v>
+        <v>3785826.0815708381</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="224" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="224"/>
-      <c r="C33" s="224"/>
-      <c r="D33" s="224"/>
-      <c r="E33" s="224"/>
-      <c r="F33" s="224"/>
-      <c r="G33" s="224"/>
-      <c r="H33" s="224"/>
-      <c r="I33" s="224"/>
-      <c r="J33" s="224"/>
-      <c r="K33" s="224"/>
-      <c r="L33" s="224"/>
+      <c r="A33" s="220" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="220"/>
+      <c r="C33" s="220"/>
+      <c r="D33" s="220"/>
+      <c r="E33" s="220"/>
+      <c r="F33" s="220"/>
+      <c r="G33" s="220"/>
+      <c r="H33" s="220"/>
+      <c r="I33" s="220"/>
+      <c r="J33" s="220"/>
+      <c r="K33" s="220"/>
+      <c r="L33" s="220"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="224"/>
-      <c r="B34" s="224"/>
-      <c r="C34" s="224"/>
-      <c r="D34" s="224"/>
-      <c r="E34" s="224"/>
-      <c r="F34" s="224"/>
-      <c r="G34" s="224"/>
-      <c r="H34" s="224"/>
-      <c r="I34" s="224"/>
-      <c r="J34" s="224"/>
-      <c r="K34" s="224"/>
-      <c r="L34" s="224"/>
+      <c r="A34" s="220"/>
+      <c r="B34" s="220"/>
+      <c r="C34" s="220"/>
+      <c r="D34" s="220"/>
+      <c r="E34" s="220"/>
+      <c r="F34" s="220"/>
+      <c r="G34" s="220"/>
+      <c r="H34" s="220"/>
+      <c r="I34" s="220"/>
+      <c r="J34" s="220"/>
+      <c r="K34" s="220"/>
+      <c r="L34" s="220"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="224"/>
-      <c r="B35" s="224"/>
-      <c r="C35" s="224"/>
-      <c r="D35" s="224"/>
-      <c r="E35" s="224"/>
-      <c r="F35" s="224"/>
-      <c r="G35" s="224"/>
-      <c r="H35" s="224"/>
-      <c r="I35" s="224"/>
-      <c r="J35" s="224"/>
-      <c r="K35" s="224"/>
-      <c r="L35" s="224"/>
+      <c r="A35" s="220"/>
+      <c r="B35" s="220"/>
+      <c r="C35" s="220"/>
+      <c r="D35" s="220"/>
+      <c r="E35" s="220"/>
+      <c r="F35" s="220"/>
+      <c r="G35" s="220"/>
+      <c r="H35" s="220"/>
+      <c r="I35" s="220"/>
+      <c r="J35" s="220"/>
+      <c r="K35" s="220"/>
+      <c r="L35" s="220"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="224"/>
-      <c r="B36" s="224"/>
-      <c r="C36" s="224"/>
-      <c r="D36" s="224"/>
-      <c r="E36" s="224"/>
-      <c r="F36" s="224"/>
-      <c r="G36" s="224"/>
-      <c r="H36" s="224"/>
-      <c r="I36" s="224"/>
-      <c r="J36" s="224"/>
-      <c r="K36" s="224"/>
-      <c r="L36" s="224"/>
+      <c r="A36" s="220"/>
+      <c r="B36" s="220"/>
+      <c r="C36" s="220"/>
+      <c r="D36" s="220"/>
+      <c r="E36" s="220"/>
+      <c r="F36" s="220"/>
+      <c r="G36" s="220"/>
+      <c r="H36" s="220"/>
+      <c r="I36" s="220"/>
+      <c r="J36" s="220"/>
+      <c r="K36" s="220"/>
+      <c r="L36" s="220"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3673,113 +3684,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="226" t="s">
+      <c r="A1" s="222" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="228"/>
+      <c r="B1" s="223"/>
+      <c r="C1" s="223"/>
+      <c r="D1" s="223"/>
+      <c r="E1" s="223"/>
+      <c r="F1" s="223"/>
+      <c r="G1" s="223"/>
+      <c r="H1" s="223"/>
+      <c r="I1" s="223"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="223"/>
+      <c r="L1" s="223"/>
+      <c r="M1" s="223"/>
+      <c r="N1" s="224"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="177"/>
-      <c r="J2" s="177"/>
-      <c r="K2" s="177"/>
-      <c r="L2" s="177"/>
-      <c r="M2" s="177"/>
-      <c r="N2" s="177"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="177"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="176"/>
+      <c r="M2" s="176"/>
+      <c r="N2" s="176"/>
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="177"/>
-      <c r="K3" s="177"/>
-      <c r="L3" s="177"/>
-      <c r="M3" s="177"/>
-      <c r="N3" s="177"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="176"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="176"/>
+      <c r="L3" s="176"/>
+      <c r="M3" s="176"/>
+      <c r="N3" s="176"/>
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="177" t="s">
+      <c r="C4" s="178"/>
+      <c r="D4" s="178"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178"/>
+      <c r="G4" s="178"/>
+      <c r="H4" s="177"/>
+      <c r="I4" s="176" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="177"/>
-      <c r="K4" s="177"/>
-      <c r="L4" s="177"/>
-      <c r="M4" s="177"/>
-      <c r="N4" s="177"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="176"/>
+      <c r="N4" s="176"/>
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
-      <c r="H5" s="178"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="177"/>
-      <c r="M5" s="177"/>
-      <c r="N5" s="177"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="178"/>
+      <c r="G5" s="178"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="176"/>
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
-      <c r="C6" s="177"/>
+      <c r="C6" s="176"/>
       <c r="D6" s="28"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="177"/>
-      <c r="K6" s="177"/>
-      <c r="L6" s="177"/>
-      <c r="M6" s="177"/>
-      <c r="N6" s="177"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="176"/>
+      <c r="K6" s="176"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="176"/>
+      <c r="N6" s="176"/>
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
@@ -3788,25 +3799,25 @@
       <c r="B7" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="213">
-        <v>265595.11</v>
+      <c r="C7" s="229">
+        <v>510646.76</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="177"/>
-      <c r="F7" s="177" t="s">
+      <c r="E7" s="176"/>
+      <c r="F7" s="176" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="177"/>
-      <c r="H7" s="178"/>
-      <c r="I7" s="177"/>
-      <c r="J7" s="177" t="str">
+      <c r="G7" s="176"/>
+      <c r="H7" s="177"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="176" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 14/07</v>
       </c>
-      <c r="K7" s="177"/>
-      <c r="L7" s="177"/>
-      <c r="M7" s="177"/>
-      <c r="N7" s="177"/>
+      <c r="K7" s="176"/>
+      <c r="L7" s="176"/>
+      <c r="M7" s="176"/>
+      <c r="N7" s="176"/>
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
@@ -3824,13 +3835,13 @@
       <c r="J8" s="80"/>
       <c r="K8" s="88">
         <f>C8-J38</f>
-        <v>-159634.85269999999</v>
-      </c>
-      <c r="L8" s="230">
+        <v>-227016.12285000001</v>
+      </c>
+      <c r="L8" s="226">
         <f>C7-J38</f>
-        <v>105960.2573</v>
-      </c>
-      <c r="M8" s="230"/>
+        <v>283630.63714999997</v>
+      </c>
+      <c r="M8" s="226"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -3897,42 +3908,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F10" s="104">
-        <v>3008.7</v>
+        <v>3122.7</v>
       </c>
       <c r="G10" s="105">
-        <v>3122.7</v>
+        <v>3448</v>
       </c>
       <c r="H10" s="106">
         <f>G10-F10</f>
-        <v>114</v>
+        <v>325.30000000000018</v>
       </c>
       <c r="I10" s="107">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>7.98</v>
+        <v>22.771000000000015</v>
       </c>
       <c r="J10" s="118">
         <f>M10*93.787</f>
-        <v>10691.718000000001</v>
+        <v>30508.911100000019</v>
       </c>
       <c r="K10" s="108">
         <f>K8*E10%</f>
-        <v>-8157.3409729700006</v>
+        <v>-11600.523877635002</v>
       </c>
       <c r="L10" s="129">
         <f>L$8*E10/S$12</f>
-        <v>5414.5691480300002</v>
+        <v>14493.525558365</v>
       </c>
       <c r="M10" s="109">
         <f>G10-F10</f>
-        <v>114</v>
+        <v>325.30000000000018</v>
       </c>
       <c r="N10" s="106">
         <f>J10+L10</f>
-        <v>16106.287148030002</v>
+        <v>45002.436658365019</v>
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>140593.33292903</v>
+        <v>169489.48243936503</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -3953,42 +3964,42 @@
         <v>5.09</v>
       </c>
       <c r="F11" s="104">
-        <v>3024.8</v>
+        <v>3093.6</v>
       </c>
       <c r="G11" s="105">
-        <v>3093.6</v>
+        <v>3296</v>
       </c>
       <c r="H11" s="106">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>68.799999999999727</v>
+        <v>202.40000000000009</v>
       </c>
       <c r="I11" s="107">
         <f t="shared" si="0"/>
-        <v>4.8159999999999812</v>
+        <v>14.168000000000008</v>
       </c>
       <c r="J11" s="118">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>6452.5455999999749</v>
+        <v>18982.48880000001</v>
       </c>
       <c r="K11" s="108">
         <f>K8*E11%</f>
-        <v>-8125.4140024299995</v>
+        <v>-11555.120653065002</v>
       </c>
       <c r="L11" s="129">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>5393.3770965700005</v>
+        <v>14436.799430934998</v>
       </c>
       <c r="M11" s="109">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>68.799999999999727</v>
+        <v>202.40000000000009</v>
       </c>
       <c r="N11" s="106">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>11845.922696569975</v>
+        <v>33419.28823093501</v>
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>135845.73933556996</v>
+        <v>157419.10486993502</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4009,42 +4020,42 @@
         <v>5.04</v>
       </c>
       <c r="F12" s="104">
-        <v>1270.2</v>
+        <v>1314.5</v>
       </c>
       <c r="G12" s="105">
-        <v>1314.5</v>
+        <v>1366.3</v>
       </c>
       <c r="H12" s="106">
         <f t="shared" si="1"/>
-        <v>44.299999999999955</v>
+        <v>51.799999999999955</v>
       </c>
       <c r="I12" s="107">
         <f t="shared" si="0"/>
-        <v>3.1009999999999973</v>
+        <v>3.6259999999999972</v>
       </c>
       <c r="J12" s="118">
         <f t="shared" si="2"/>
-        <v>4154.7640999999958</v>
+        <v>4858.1665999999959</v>
       </c>
       <c r="K12" s="108">
         <f>K8*E12%</f>
-        <v>-8045.5965760799991</v>
+        <v>-11441.612591640001</v>
       </c>
       <c r="L12" s="129">
         <f t="shared" si="3"/>
-        <v>5340.39696792</v>
+        <v>14294.984112359998</v>
       </c>
       <c r="M12" s="109">
         <f>G12-F12</f>
-        <v>44.299999999999955</v>
+        <v>51.799999999999955</v>
       </c>
       <c r="N12" s="106">
         <f t="shared" si="5"/>
-        <v>9495.1610679199948</v>
+        <v>19153.150712359995</v>
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>207553.91838727996</v>
+        <v>347916.00210849434</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4058,52 +4069,52 @@
       <c r="B13" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="180" t="s">
+      <c r="C13" s="179" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="181">
+      <c r="E13" s="180">
         <v>5.21</v>
       </c>
       <c r="F13" s="104">
-        <v>706.3</v>
+        <v>791.8</v>
       </c>
       <c r="G13" s="105">
-        <v>791.8</v>
+        <v>883.5</v>
       </c>
       <c r="H13" s="106">
         <f t="shared" si="1"/>
-        <v>85.5</v>
-      </c>
-      <c r="I13" s="182">
+        <v>91.700000000000045</v>
+      </c>
+      <c r="I13" s="181">
         <f t="shared" si="0"/>
-        <v>5.9850000000000003</v>
+        <v>6.419000000000004</v>
       </c>
       <c r="J13" s="118">
         <f t="shared" si="2"/>
-        <v>8018.7885000000006</v>
-      </c>
-      <c r="K13" s="183">
+        <v>8600.2679000000044</v>
+      </c>
+      <c r="K13" s="182">
         <f>K8*E13%</f>
-        <v>-8316.9758256699988</v>
+        <v>-11827.540000485002</v>
       </c>
       <c r="L13" s="129">
         <f t="shared" si="3"/>
-        <v>5520.5294053299995</v>
-      </c>
-      <c r="M13" s="184">
+        <v>14777.156195514999</v>
+      </c>
+      <c r="M13" s="183">
         <f t="shared" si="4"/>
-        <v>85.5</v>
+        <v>91.700000000000045</v>
       </c>
       <c r="N13" s="106">
         <f t="shared" si="5"/>
-        <v>13539.317905330001</v>
+        <v>23377.424095515002</v>
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>140462.50939633002</v>
+        <v>204484.61558651499</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4124,42 +4135,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F14" s="104">
-        <v>1352.4</v>
+        <v>1435.7</v>
       </c>
       <c r="G14" s="105">
-        <v>1435.7</v>
+        <v>1509.4</v>
       </c>
       <c r="H14" s="106">
         <f t="shared" si="1"/>
-        <v>83.299999999999955</v>
+        <v>73.700000000000045</v>
       </c>
       <c r="I14" s="107">
         <f t="shared" si="0"/>
-        <v>5.8309999999999977</v>
+        <v>5.1590000000000034</v>
       </c>
       <c r="J14" s="118">
         <f t="shared" si="2"/>
-        <v>7812.457099999996</v>
+        <v>6912.1019000000051</v>
       </c>
       <c r="K14" s="108">
         <f>K8*E14%</f>
-        <v>-8157.3409729700006</v>
+        <v>-11600.523877635002</v>
       </c>
       <c r="L14" s="129">
         <f t="shared" si="3"/>
-        <v>5414.5691480300002</v>
+        <v>14493.525558365</v>
       </c>
       <c r="M14" s="109">
         <f t="shared" si="4"/>
-        <v>83.299999999999955</v>
+        <v>73.700000000000045</v>
       </c>
       <c r="N14" s="106">
         <f t="shared" si="5"/>
-        <v>13227.026248029997</v>
+        <v>21405.627458365005</v>
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>214036.59964127</v>
+        <v>145892.67323936502</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4180,42 +4191,42 @@
         <v>5.09</v>
       </c>
       <c r="F15" s="104">
-        <v>2383.1999999999998</v>
+        <v>2418</v>
       </c>
       <c r="G15" s="105">
-        <v>2418</v>
+        <v>2581.1999999999998</v>
       </c>
       <c r="H15" s="106">
         <f t="shared" si="1"/>
-        <v>34.800000000000182</v>
+        <v>163.19999999999982</v>
       </c>
       <c r="I15" s="107">
         <f t="shared" si="0"/>
-        <v>2.4360000000000128</v>
+        <v>11.423999999999989</v>
       </c>
       <c r="J15" s="118">
         <f t="shared" si="2"/>
-        <v>3263.7876000000174</v>
+        <v>15306.038399999983</v>
       </c>
       <c r="K15" s="108">
         <f>K8*E15%</f>
-        <v>-8125.4140024299995</v>
+        <v>-11555.120653065002</v>
       </c>
       <c r="L15" s="129">
         <f t="shared" si="3"/>
-        <v>5393.3770965700005</v>
+        <v>14436.799430934998</v>
       </c>
       <c r="M15" s="109">
         <f t="shared" si="4"/>
-        <v>34.800000000000182</v>
+        <v>163.19999999999982</v>
       </c>
       <c r="N15" s="106">
         <f t="shared" si="5"/>
-        <v>8657.1646965700184</v>
+        <v>29742.837830934979</v>
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>132656.98133557002</v>
+        <v>153742.65446993499</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4235,42 +4246,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F16" s="104">
-        <v>1975.4</v>
+        <v>2053.3000000000002</v>
       </c>
       <c r="G16" s="105">
-        <v>2053.3000000000002</v>
+        <v>2155.5</v>
       </c>
       <c r="H16" s="106">
         <f t="shared" si="1"/>
-        <v>77.900000000000091</v>
+        <v>102.19999999999982</v>
       </c>
       <c r="I16" s="107">
         <f t="shared" si="0"/>
-        <v>5.4530000000000065</v>
+        <v>7.1539999999999884</v>
       </c>
       <c r="J16" s="118">
         <f t="shared" si="2"/>
-        <v>7306.0073000000093</v>
+        <v>9585.0313999999835</v>
       </c>
       <c r="K16" s="108">
         <f>K8*E16%</f>
-        <v>-8157.3409729700006</v>
+        <v>-11600.523877635002</v>
       </c>
       <c r="L16" s="129">
         <f t="shared" si="3"/>
-        <v>5414.5691480300002</v>
+        <v>14493.525558365</v>
       </c>
       <c r="M16" s="109">
         <f t="shared" si="4"/>
-        <v>77.900000000000091</v>
+        <v>102.19999999999982</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" si="5"/>
-        <v>12720.576448030009</v>
+        <v>24078.556958364985</v>
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>137207.62222903001</v>
+        <v>148565.60273936499</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4280,52 +4291,52 @@
       <c r="B17" s="91">
         <v>9</v>
       </c>
-      <c r="C17" s="197" t="s">
+      <c r="C17" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="198" t="s">
+      <c r="D17" s="195" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="199">
+      <c r="E17" s="196">
         <v>5.09</v>
       </c>
-      <c r="F17" s="200">
-        <v>3022.6</v>
-      </c>
-      <c r="G17" s="201">
+      <c r="F17" s="197">
         <v>3139.2</v>
       </c>
-      <c r="H17" s="202">
+      <c r="G17" s="198">
+        <v>3253.7</v>
+      </c>
+      <c r="H17" s="199">
         <f t="shared" si="1"/>
-        <v>116.59999999999991</v>
-      </c>
-      <c r="I17" s="203">
+        <v>114.5</v>
+      </c>
+      <c r="I17" s="200">
         <f t="shared" si="0"/>
-        <v>8.1619999999999937</v>
-      </c>
-      <c r="J17" s="204">
+        <v>8.0150000000000006</v>
+      </c>
+      <c r="J17" s="201">
         <f t="shared" si="2"/>
-        <v>10935.564199999992</v>
-      </c>
-      <c r="K17" s="205">
+        <v>10738.611500000001</v>
+      </c>
+      <c r="K17" s="202">
         <f>K8*E17%</f>
-        <v>-8125.4140024299995</v>
-      </c>
-      <c r="L17" s="206">
+        <v>-11555.120653065002</v>
+      </c>
+      <c r="L17" s="203">
         <f t="shared" si="3"/>
-        <v>5393.3770965700005</v>
-      </c>
-      <c r="M17" s="207">
+        <v>14436.799430934998</v>
+      </c>
+      <c r="M17" s="204">
         <f t="shared" si="4"/>
-        <v>116.59999999999991</v>
-      </c>
-      <c r="N17" s="202">
+        <v>114.5</v>
+      </c>
+      <c r="N17" s="199">
         <f t="shared" si="5"/>
-        <v>16328.941296569992</v>
+        <v>25175.410930934999</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>494330.45710233197</v>
+        <v>646296.80400792742</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4345,42 +4356,42 @@
         <v>5.04</v>
       </c>
       <c r="F18" s="104">
-        <v>1692.8</v>
+        <v>1790</v>
       </c>
       <c r="G18" s="105">
-        <v>1790</v>
+        <v>1888.2</v>
       </c>
       <c r="H18" s="106">
         <f t="shared" si="1"/>
-        <v>97.200000000000045</v>
+        <v>98.200000000000045</v>
       </c>
       <c r="I18" s="107">
         <f t="shared" si="0"/>
-        <v>6.8040000000000038</v>
+        <v>6.8740000000000041</v>
       </c>
       <c r="J18" s="118">
         <f t="shared" si="2"/>
-        <v>9116.096400000004</v>
+        <v>9209.8834000000043</v>
       </c>
       <c r="K18" s="108">
         <f>K8*E18%</f>
-        <v>-8045.5965760799991</v>
+        <v>-11441.612591640001</v>
       </c>
       <c r="L18" s="129">
         <f t="shared" si="3"/>
-        <v>5340.39696792</v>
+        <v>14294.984112359998</v>
       </c>
       <c r="M18" s="109">
         <f t="shared" si="4"/>
-        <v>97.200000000000045</v>
+        <v>98.200000000000045</v>
       </c>
       <c r="N18" s="106">
         <f t="shared" si="5"/>
-        <v>14456.493367920004</v>
+        <v>23504.867512360004</v>
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>137238.23715191998</v>
+        <v>146286.61129636</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4400,42 +4411,42 @@
         <v>5.21</v>
       </c>
       <c r="F19" s="104">
-        <v>2773.4</v>
+        <v>2998.2</v>
       </c>
       <c r="G19" s="105">
-        <v>2998.2</v>
+        <v>3235.4</v>
       </c>
       <c r="H19" s="106">
         <f t="shared" si="1"/>
-        <v>224.79999999999973</v>
+        <v>237.20000000000027</v>
       </c>
       <c r="I19" s="107">
         <f t="shared" si="0"/>
-        <v>15.735999999999983</v>
+        <v>16.604000000000021</v>
       </c>
       <c r="J19" s="118">
         <f t="shared" si="2"/>
-        <v>21083.317599999977</v>
+        <v>22246.276400000028</v>
       </c>
       <c r="K19" s="108">
         <f>K8*E19%</f>
-        <v>-8316.9758256699988</v>
+        <v>-11827.540000485002</v>
       </c>
       <c r="L19" s="129">
         <f t="shared" si="3"/>
-        <v>5520.5294053299995</v>
+        <v>14777.156195514999</v>
       </c>
       <c r="M19" s="109">
         <f>G19-F19</f>
-        <v>224.79999999999973</v>
+        <v>237.20000000000027</v>
       </c>
       <c r="N19" s="106">
         <f t="shared" si="5"/>
-        <v>26603.847005329975</v>
+        <v>37023.432595515027</v>
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>153527.03849632997</v>
+        <v>163946.62408651505</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4455,42 +4466,42 @@
         <v>5.1100000000000003</v>
       </c>
       <c r="F20" s="104">
-        <v>4496.3</v>
+        <v>4665.5</v>
       </c>
       <c r="G20" s="105">
-        <v>4665.5</v>
+        <v>4902.5</v>
       </c>
       <c r="H20" s="106">
         <f t="shared" si="1"/>
-        <v>169.19999999999982</v>
+        <v>237</v>
       </c>
       <c r="I20" s="107">
         <f t="shared" si="0"/>
-        <v>11.843999999999989</v>
+        <v>16.59</v>
       </c>
       <c r="J20" s="118">
         <f t="shared" si="2"/>
-        <v>15868.760399999985</v>
+        <v>22227.519</v>
       </c>
       <c r="K20" s="108">
         <f>K8*E20%</f>
-        <v>-8157.3409729700006</v>
+        <v>-11600.523877635002</v>
       </c>
       <c r="L20" s="129">
         <f t="shared" si="3"/>
-        <v>5414.5691480300002</v>
+        <v>14493.525558365</v>
       </c>
       <c r="M20" s="109">
         <f t="shared" si="4"/>
-        <v>169.19999999999982</v>
+        <v>237</v>
       </c>
       <c r="N20" s="106">
         <f t="shared" si="5"/>
-        <v>21283.329548029986</v>
+        <v>36721.044558365</v>
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>145770.37532902998</v>
+        <v>161208.09033936501</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4513,39 +4524,39 @@
         <v>3467.1</v>
       </c>
       <c r="G21" s="105">
-        <v>3467.1</v>
+        <v>3467.7</v>
       </c>
       <c r="H21" s="106">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.59999999999990905</v>
       </c>
       <c r="I21" s="107">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.199999999999364E-2</v>
       </c>
       <c r="J21" s="118">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>56.272199999991471</v>
       </c>
       <c r="K21" s="108">
         <f>K8*E21%</f>
-        <v>-8125.4140024299995</v>
+        <v>-11555.120653065002</v>
       </c>
       <c r="L21" s="129">
         <f t="shared" si="3"/>
-        <v>5393.3770965700005</v>
+        <v>14436.799430934998</v>
       </c>
       <c r="M21" s="109">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.59999999999990905</v>
       </c>
       <c r="N21" s="106">
         <f t="shared" si="5"/>
-        <v>5393.3770965700005</v>
+        <v>14493.07163093499</v>
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>205417.00304013002</v>
+        <v>255316.71042526618</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4565,42 +4576,42 @@
         <v>5.04</v>
       </c>
       <c r="F22" s="104">
-        <v>2015.9</v>
+        <v>2097.9</v>
       </c>
       <c r="G22" s="105">
-        <v>2097.9</v>
+        <v>2198.0500000000002</v>
       </c>
       <c r="H22" s="106">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>100.15000000000009</v>
       </c>
       <c r="I22" s="107">
         <f t="shared" si="0"/>
-        <v>5.74</v>
+        <v>7.0105000000000066</v>
       </c>
       <c r="J22" s="118">
         <f t="shared" si="2"/>
-        <v>7690.5340000000006</v>
+        <v>9392.7680500000097</v>
       </c>
       <c r="K22" s="108">
         <f>K8*E22%</f>
-        <v>-8045.5965760799991</v>
+        <v>-11441.612591640001</v>
       </c>
       <c r="L22" s="129">
         <f t="shared" si="3"/>
-        <v>5340.39696792</v>
+        <v>14294.984112359998</v>
       </c>
       <c r="M22" s="109">
         <f t="shared" si="4"/>
-        <v>82</v>
+        <v>100.15000000000009</v>
       </c>
       <c r="N22" s="106">
         <f t="shared" si="5"/>
-        <v>13030.930967920001</v>
+        <v>23687.752162360008</v>
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>135812.67475191999</v>
+        <v>274162.50948171999</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4620,42 +4631,42 @@
         <v>5.21</v>
       </c>
       <c r="F23" s="104">
-        <v>4072.7</v>
+        <v>4222.8</v>
       </c>
       <c r="G23" s="105">
-        <v>4222.8</v>
+        <v>4358.6000000000004</v>
       </c>
       <c r="H23" s="106">
         <f t="shared" si="1"/>
-        <v>150.10000000000036</v>
+        <v>135.80000000000018</v>
       </c>
       <c r="I23" s="107">
         <f t="shared" si="0"/>
-        <v>10.507000000000026</v>
+        <v>9.5060000000000144</v>
       </c>
       <c r="J23" s="118">
         <f t="shared" si="2"/>
-        <v>14077.428700000035</v>
+        <v>12736.274600000017</v>
       </c>
       <c r="K23" s="108">
         <f>K8*E23%</f>
-        <v>-8316.9758256699988</v>
+        <v>-11827.540000485002</v>
       </c>
       <c r="L23" s="129">
         <f t="shared" si="3"/>
-        <v>5520.5294053299995</v>
+        <v>14777.156195514999</v>
       </c>
       <c r="M23" s="109">
         <f t="shared" si="4"/>
-        <v>150.10000000000036</v>
+        <v>135.80000000000018</v>
       </c>
       <c r="N23" s="106">
         <f t="shared" si="5"/>
-        <v>19597.958105330035</v>
+        <v>27513.430795515014</v>
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>224337.26874697005</v>
+        <v>208620.62228651502</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4675,42 +4686,42 @@
         <v>5.04</v>
       </c>
       <c r="F24" s="104">
-        <v>1462.2</v>
+        <v>1529.3</v>
       </c>
       <c r="G24" s="105">
-        <v>1529.3</v>
+        <v>1563.2</v>
       </c>
       <c r="H24" s="106">
         <f t="shared" si="1"/>
-        <v>67.099999999999909</v>
+        <v>33.900000000000091</v>
       </c>
       <c r="I24" s="107">
         <f t="shared" si="0"/>
-        <v>4.6969999999999938</v>
+        <v>2.3730000000000064</v>
       </c>
       <c r="J24" s="118">
         <f t="shared" si="2"/>
-        <v>6293.1076999999923</v>
+        <v>3179.3793000000087</v>
       </c>
       <c r="K24" s="108">
         <f>K8*E24%</f>
-        <v>-8045.5965760799991</v>
+        <v>-11441.612591640001</v>
       </c>
       <c r="L24" s="129">
         <f t="shared" si="3"/>
-        <v>5340.39696792</v>
+        <v>14294.984112359998</v>
       </c>
       <c r="M24" s="109">
         <f t="shared" si="4"/>
-        <v>67.099999999999909</v>
+        <v>33.900000000000091</v>
       </c>
       <c r="N24" s="106">
         <f t="shared" si="5"/>
-        <v>11633.504667919991</v>
+        <v>17474.363412360006</v>
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>134415.24845191999</v>
+        <v>140256.10719636001</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -4730,42 +4741,42 @@
         <v>5.21</v>
       </c>
       <c r="F25" s="104">
-        <v>1352.5</v>
+        <v>1452.3</v>
       </c>
       <c r="G25" s="105">
-        <v>1452.3</v>
+        <v>1527.7</v>
       </c>
       <c r="H25" s="106">
         <f t="shared" si="1"/>
-        <v>99.799999999999955</v>
+        <v>75.400000000000091</v>
       </c>
       <c r="I25" s="107">
         <f t="shared" si="0"/>
-        <v>6.9859999999999971</v>
+        <v>5.2780000000000067</v>
       </c>
       <c r="J25" s="118">
         <f t="shared" si="2"/>
-        <v>9359.9425999999967</v>
+        <v>7071.5398000000087</v>
       </c>
       <c r="K25" s="108">
         <f>K8*E25%</f>
-        <v>-8316.9758256699988</v>
+        <v>-11827.540000485002</v>
       </c>
       <c r="L25" s="129">
         <f t="shared" si="3"/>
-        <v>5520.5294053299995</v>
+        <v>14777.156195514999</v>
       </c>
       <c r="M25" s="109">
         <f t="shared" si="4"/>
-        <v>99.799999999999955</v>
+        <v>75.400000000000091</v>
       </c>
       <c r="N25" s="106">
         <f t="shared" si="5"/>
-        <v>14880.472005329997</v>
+        <v>21848.695995515009</v>
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>141803.66349633</v>
+        <v>148771.88748651501</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4785,42 +4796,42 @@
         <v>7.4</v>
       </c>
       <c r="F26" s="104">
-        <v>7102.6</v>
+        <v>7289.3</v>
       </c>
       <c r="G26" s="105">
-        <v>7289.3</v>
+        <v>7666.8</v>
       </c>
       <c r="H26" s="106">
         <f t="shared" si="1"/>
-        <v>186.69999999999982</v>
+        <v>377.5</v>
       </c>
       <c r="I26" s="107">
         <f t="shared" si="0"/>
-        <v>13.068999999999988</v>
+        <v>26.425000000000004</v>
       </c>
       <c r="J26" s="118">
         <f t="shared" si="2"/>
-        <v>17510.032899999984</v>
+        <v>35404.592499999999</v>
       </c>
       <c r="K26" s="108">
         <f>K8*E26%</f>
-        <v>-11812.979099800001</v>
+        <v>-16799.193090900004</v>
       </c>
       <c r="L26" s="129">
         <f t="shared" si="3"/>
-        <v>7841.0590401999998</v>
+        <v>20988.667149099998</v>
       </c>
       <c r="M26" s="109">
         <f t="shared" si="4"/>
-        <v>186.69999999999982</v>
+        <v>377.5</v>
       </c>
       <c r="N26" s="106">
         <f>J26+L26</f>
-        <v>25351.091940199985</v>
+        <v>56393.2596491</v>
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>205625.87448019997</v>
+        <v>236668.0421891</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4830,41 +4841,41 @@
       <c r="B27" s="92">
         <v>19</v>
       </c>
-      <c r="C27" s="208" t="s">
+      <c r="C27" s="205" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="209" t="s">
+      <c r="D27" s="206" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="210">
+      <c r="E27" s="207">
         <v>1.08</v>
       </c>
-      <c r="F27" s="200"/>
-      <c r="G27" s="201"/>
-      <c r="H27" s="202">
+      <c r="F27" s="197"/>
+      <c r="G27" s="198"/>
+      <c r="H27" s="199">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="203">
+      <c r="I27" s="200">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="204"/>
-      <c r="K27" s="205"/>
-      <c r="L27" s="206">
+      <c r="J27" s="201"/>
+      <c r="K27" s="202"/>
+      <c r="L27" s="203">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
-      </c>
-      <c r="M27" s="207">
-        <v>0</v>
-      </c>
-      <c r="N27" s="202">
+        <v>3063.2108812199999</v>
+      </c>
+      <c r="M27" s="204">
+        <v>0</v>
+      </c>
+      <c r="N27" s="199">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>102567.08926021976</v>
+        <v>134853.21176985494</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4872,7 +4883,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="92"/>
-      <c r="C28" s="185" t="s">
+      <c r="C28" s="184" t="s">
         <v>68</v>
       </c>
       <c r="D28" s="104"/>
@@ -4884,64 +4895,64 @@
       <c r="H28" s="106">
         <v>0</v>
       </c>
-      <c r="I28" s="186">
+      <c r="I28" s="185">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="187"/>
+      <c r="J28" s="186"/>
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M28" s="109">
         <v>0</v>
       </c>
       <c r="N28" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>43585.533061559996</v>
+        <v>40605.584549220002</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
-      <c r="C29" s="174" t="s">
+      <c r="C29" s="173" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153">
+      <c r="D29" s="152"/>
+      <c r="E29" s="152">
         <v>1.08</v>
       </c>
-      <c r="F29" s="153"/>
-      <c r="G29" s="153"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="175"/>
-      <c r="J29" s="176"/>
-      <c r="K29" s="155"/>
-      <c r="L29" s="156">
+      <c r="F29" s="152"/>
+      <c r="G29" s="152"/>
+      <c r="H29" s="153"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="175"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="155">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
-      </c>
-      <c r="M29" s="157">
-        <v>0</v>
-      </c>
-      <c r="N29" s="154">
+        <v>3063.2108812199999</v>
+      </c>
+      <c r="M29" s="156">
+        <v>0</v>
+      </c>
+      <c r="N29" s="153">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>102567.08926021976</v>
+        <v>134853.21176985494</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
-      <c r="C30" s="185" t="s">
+      <c r="C30" s="184" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="104"/>
@@ -4951,29 +4962,29 @@
       <c r="F30" s="104"/>
       <c r="G30" s="104"/>
       <c r="H30" s="106"/>
-      <c r="I30" s="186"/>
-      <c r="J30" s="187"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="186"/>
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M30" s="109">
         <v>0</v>
       </c>
       <c r="N30" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>43585.533061559996</v>
+        <v>73512.393323248791</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
-      <c r="C31" s="185" t="s">
+      <c r="C31" s="184" t="s">
         <v>71</v>
       </c>
       <c r="D31" s="104"/>
@@ -4983,23 +4994,23 @@
       <c r="F31" s="104"/>
       <c r="G31" s="104"/>
       <c r="H31" s="106"/>
-      <c r="I31" s="186"/>
-      <c r="J31" s="187"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="186"/>
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M31" s="109">
         <v>0</v>
       </c>
       <c r="N31" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>27454.744446839999</v>
+        <v>29373.584549219999</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -5020,18 +5031,18 @@
       <c r="K32" s="115"/>
       <c r="L32" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M32" s="109">
         <v>0</v>
       </c>
       <c r="N32" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>43585.533061559996</v>
+        <v>29373.584549219999</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -5052,18 +5063,18 @@
       <c r="K33" s="115"/>
       <c r="L33" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M33" s="109">
         <v>0</v>
       </c>
       <c r="N33" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>27454.744446839999</v>
+        <v>29373.584549219999</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -5084,18 +5095,18 @@
       <c r="K34" s="115"/>
       <c r="L34" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M34" s="109">
         <v>0</v>
       </c>
       <c r="N34" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>27454.744446839999</v>
+        <v>29373.584549219999</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5103,7 +5114,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="92"/>
-      <c r="C35" s="185" t="s">
+      <c r="C35" s="184" t="s">
         <v>75</v>
       </c>
       <c r="D35" s="104"/>
@@ -5115,26 +5126,26 @@
       <c r="H35" s="106">
         <v>0</v>
       </c>
-      <c r="I35" s="186">
+      <c r="I35" s="185">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="212"/>
+      <c r="J35" s="209"/>
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M35" s="109">
         <v>0</v>
       </c>
       <c r="N35" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>43585.533061559996</v>
+        <v>29373.584549219999</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5142,7 +5153,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="92"/>
-      <c r="C36" s="185" t="s">
+      <c r="C36" s="184" t="s">
         <v>76</v>
       </c>
       <c r="D36" s="104"/>
@@ -5154,26 +5165,26 @@
       <c r="H36" s="106">
         <v>0</v>
       </c>
-      <c r="I36" s="186">
+      <c r="I36" s="185">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="212"/>
+      <c r="J36" s="209"/>
       <c r="K36" s="108"/>
       <c r="L36" s="129">
         <f t="shared" si="3"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="M36" s="109">
         <v>0</v>
       </c>
       <c r="N36" s="106">
         <f t="shared" si="6"/>
-        <v>1144.37077884</v>
+        <v>3063.2108812199999</v>
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>27454.744446839999</v>
+        <v>56736.373163939999</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5220,17 +5231,17 @@
       <c r="I38" s="114"/>
       <c r="J38" s="119">
         <f>SUM(J10:J37)</f>
-        <v>159634.85269999999</v>
+        <v>227016.12285000001</v>
       </c>
       <c r="K38" s="115"/>
       <c r="L38" s="115">
         <f>SUM(L10:L37)</f>
-        <v>105960.25730000007</v>
+        <v>283630.63715000002</v>
       </c>
       <c r="M38" s="116"/>
       <c r="N38" s="112">
         <f>SUM(N10:N37)</f>
-        <v>265595.10999999993</v>
+        <v>510646.76000000013</v>
       </c>
       <c r="P38" s="44"/>
     </row>
@@ -5247,13 +5258,13 @@
       <c r="H39" s="95"/>
       <c r="I39" s="96">
         <f>SUM(I10:I38)</f>
-        <v>119.14699999999996</v>
+        <v>169.43850000000009</v>
       </c>
       <c r="J39" s="128"/>
       <c r="K39" s="96"/>
       <c r="L39" s="135">
         <f>L38+J38</f>
-        <v>265595.11000000004</v>
+        <v>510646.76</v>
       </c>
       <c r="M39" s="95"/>
       <c r="N39" s="95"/>
@@ -5263,18 +5274,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="229"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="227"/>
-      <c r="F40" s="227"/>
-      <c r="G40" s="227"/>
-      <c r="H40" s="227"/>
-      <c r="I40" s="227"/>
-      <c r="J40" s="227"/>
-      <c r="K40" s="227"/>
-      <c r="L40" s="227"/>
-      <c r="M40" s="227"/>
-      <c r="N40" s="227"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="223"/>
+      <c r="E40" s="223"/>
+      <c r="F40" s="223"/>
+      <c r="G40" s="223"/>
+      <c r="H40" s="223"/>
+      <c r="I40" s="223"/>
+      <c r="J40" s="223"/>
+      <c r="K40" s="223"/>
+      <c r="L40" s="223"/>
+      <c r="M40" s="223"/>
+      <c r="N40" s="223"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -5288,20 +5299,20 @@
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L44" s="158"/>
+      <c r="L44" s="157"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L45" s="98"/>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E46" s="159"/>
-      <c r="F46" s="159"/>
-      <c r="G46" s="159"/>
-      <c r="H46" s="159"/>
-      <c r="I46" s="159"/>
-      <c r="J46" s="159"/>
-      <c r="K46" s="159"/>
-      <c r="L46" s="160"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="158"/>
+      <c r="H46" s="158"/>
+      <c r="I46" s="158"/>
+      <c r="J46" s="158"/>
+      <c r="K46" s="158"/>
+      <c r="L46" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="3">
